--- a/Diseno/Nuptimizer-PerfilNutricional.xlsx
+++ b/Diseno/Nuptimizer-PerfilNutricional.xlsx
@@ -33,38 +33,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="2">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="2">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,75 +385,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -819,9 +718,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="14" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A1" s="14"/>
       <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
@@ -829,9 +726,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
       <c r="F1" s="19"/>
-      <c r="G1" s="17" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
+      <c r="G1" s="17"/>
       <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
